--- a/5/search/FY3_Missile1_results/solutions_direction_72.0.xlsx
+++ b/5/search/FY3_Missile1_results/solutions_direction_72.0.xlsx
@@ -517,7 +517,7 @@
         <v>700</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8999999999999986</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
